--- a/docs/属性词条对照表.xlsx
+++ b/docs/属性词条对照表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GPUGC\the_law_of_infinite_genes\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D31113A-704D-447D-8BAB-BD190557D3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1BAEF3-5D8C-4418-80FB-2CABC421DF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30624" yWindow="-6420" windowWidth="17472" windowHeight="20316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30528" yWindow="-6420" windowWidth="17472" windowHeight="20316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -154,6 +154,41 @@
   <si>
     <t>中文描述</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DodgeChance</t>
+  </si>
+  <si>
+    <t>闪避率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeckillChance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>秒杀率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecoilPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后坐力百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReloadTimePct</t>
+  </si>
+  <si>
+    <t>换弹时间百分比</t>
+  </si>
+  <si>
+    <t>ShootSpeedScale</t>
+  </si>
+  <si>
+    <t>射速百分比</t>
   </si>
 </sst>
 </file>
@@ -196,9 +231,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -479,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.5" customWidth="1"/>
@@ -515,10 +549,10 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
     </row>
@@ -532,10 +566,10 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
     </row>
@@ -549,10 +583,10 @@
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>-100000000</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>100000000</v>
       </c>
     </row>
@@ -566,10 +600,10 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>100000000</v>
       </c>
     </row>
@@ -583,10 +617,10 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>-100000000</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>100000000</v>
       </c>
     </row>
@@ -600,10 +634,10 @@
       <c r="C7">
         <v>0</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>100000000</v>
       </c>
     </row>
@@ -617,10 +651,10 @@
       <c r="C8">
         <v>0</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>100000000</v>
       </c>
     </row>
@@ -634,10 +668,10 @@
       <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>100000000</v>
       </c>
     </row>
@@ -651,10 +685,10 @@
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>-100000000</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>100000000</v>
       </c>
     </row>
@@ -668,10 +702,10 @@
       <c r="C11">
         <v>0</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>-100000000</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>100000000</v>
       </c>
     </row>
@@ -685,10 +719,10 @@
       <c r="C12">
         <v>0</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>-100000000</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>100000000</v>
       </c>
     </row>
@@ -702,10 +736,10 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>-100000000</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>100000000</v>
       </c>
     </row>
@@ -719,10 +753,10 @@
       <c r="C14">
         <v>1</v>
       </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>100000000</v>
       </c>
     </row>
@@ -736,10 +770,10 @@
       <c r="C15">
         <v>0</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <v>100000000</v>
       </c>
     </row>
@@ -753,10 +787,10 @@
       <c r="C16">
         <v>0</v>
       </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>1</v>
       </c>
     </row>
@@ -770,10 +804,10 @@
       <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
         <v>100000000</v>
       </c>
     </row>
@@ -787,15 +821,101 @@
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18">
         <v>-100000000</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>-1</v>
+      </c>
+      <c r="E21">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>-1</v>
+      </c>
+      <c r="E22">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>-1</v>
+      </c>
+      <c r="E23">
         <v>100000000</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>